--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_12.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_12.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>StudySubject</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Interesting</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.3966539985626891</v>
+        <v>1.255151992572123</v>
       </c>
       <c r="C2">
-        <v>1.208763137617202</v>
+        <v>-1.078020103730558</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.172679025415917</v>
+        <v>-0.9446181892789189</v>
       </c>
       <c r="C3">
-        <v>0.4469165161729383</v>
+        <v>0.8091582621515767</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.002583876847741942</v>
+        <v>0.9130549006288898</v>
       </c>
       <c r="C4">
-        <v>-0.7627999490068109</v>
+        <v>-1.483775245783605</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.09590811163827943</v>
+        <v>0.5827335770326653</v>
       </c>
       <c r="C5">
-        <v>1.160046594759354</v>
+        <v>-0.4231951479557582</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.3733151259174398</v>
+        <v>2.06479866772017</v>
       </c>
       <c r="C6">
-        <v>-0.2758525132879733</v>
+        <v>-2.092899157073469</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.1664271879111046</v>
+        <v>1.304745901849027</v>
       </c>
       <c r="C7">
-        <v>-0.6996899062876559</v>
+        <v>-1.571195775205853</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.7511548385037378</v>
+        <v>-0.8112717692931054</v>
       </c>
       <c r="C8">
-        <v>0.263538328571356</v>
+        <v>1.020041997805163</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.4651373877091337</v>
+        <v>-1.157805305545595</v>
       </c>
       <c r="C9">
-        <v>-0.269176559574728</v>
+        <v>0.398221754572506</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.5128239067677224</v>
+        <v>0.1577391930773093</v>
       </c>
       <c r="C10">
-        <v>0.502452266235117</v>
+        <v>-0.03843638512759358</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.03121281133029418</v>
+        <v>-1.424292373664284</v>
       </c>
       <c r="C11">
-        <v>1.199760335805293</v>
+        <v>0.7454036369331299</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.418876246063817</v>
+        <v>-0.2362098840150962</v>
       </c>
       <c r="C12">
-        <v>-0.5131969950979677</v>
+        <v>0.4839676425466545</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.2486939705547009</v>
+        <v>0.4418773144510089</v>
       </c>
       <c r="C13">
-        <v>-0.5428757577417829</v>
+        <v>-0.4983850387606251</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.3573135220223371</v>
+        <v>0.4511003916364153</v>
       </c>
       <c r="C14">
-        <v>-0.2911965498947532</v>
+        <v>0.1425644575208856</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.4094109426935143</v>
+        <v>-0.7484843748514355</v>
       </c>
       <c r="C15">
-        <v>-1.829294637760867</v>
+        <v>0.2093480400407718</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.189015793025964</v>
+        <v>-0.9312514860016572</v>
       </c>
       <c r="C16">
-        <v>3.170826481543104</v>
+        <v>1.240980460324524</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.740979333808527</v>
+        <v>0.2174090111956944</v>
       </c>
       <c r="C17">
-        <v>-0.6649428771364421</v>
+        <v>-0.7044434331079608</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.019514148345652</v>
+        <v>1.483016596865718</v>
       </c>
       <c r="C18">
-        <v>0.8973478391027793</v>
+        <v>-1.532821123321913</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.1960317652624601</v>
+        <v>1.156494546095025</v>
       </c>
       <c r="C19">
-        <v>-1.680868710670226</v>
+        <v>-0.9062307598384833</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.180705340796595</v>
+        <v>-1.035375457909668</v>
       </c>
       <c r="C20">
-        <v>-0.9585720196521967</v>
+        <v>2.090370522959138</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.1872490905019633</v>
+        <v>0.2000834094213439</v>
       </c>
       <c r="C21">
-        <v>-0.6907934297389705</v>
+        <v>0.5160959864612102</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.187763190919121</v>
+        <v>0.8948931408432265</v>
       </c>
       <c r="C22">
-        <v>-0.2254609431259122</v>
+        <v>-1.203870414754631</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.2698413865056678</v>
+        <v>-0.1722120728112915</v>
       </c>
       <c r="C23">
-        <v>0.580882311291538</v>
+        <v>-0.5841112351684637</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.8450157752363572</v>
+        <v>0.3236510294406406</v>
       </c>
       <c r="C24">
-        <v>0.2894424398248596</v>
+        <v>-1.23511738168214</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-1.099048861585278</v>
+        <v>-0.5633022982764245</v>
       </c>
       <c r="C25">
-        <v>-0.03488328519278089</v>
+        <v>0.04768544978263692</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.5032196475347651</v>
+        <v>0.2251261106079069</v>
       </c>
       <c r="C26">
-        <v>-0.2762578042185902</v>
+        <v>0.2895592592029089</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.538468930548591</v>
+        <v>1.684742449719243</v>
       </c>
       <c r="C27">
-        <v>-2.178814358830337</v>
+        <v>1.307117542626767</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-1.027175992186131</v>
+        <v>1.524402514598243</v>
       </c>
       <c r="C28">
-        <v>0.09783919784145667</v>
+        <v>-1.145892782908074</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.396490425802131</v>
+        <v>1.433011279563727</v>
       </c>
       <c r="C29">
-        <v>1.317089348981404</v>
+        <v>0.5412681290630104</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.4597222980054825</v>
+        <v>-0.00445443380457741</v>
       </c>
       <c r="C30">
-        <v>0.1795401694858401</v>
+        <v>-1.207263019764245</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.4349314977254188</v>
+        <v>0.04106574345323614</v>
       </c>
       <c r="C31">
-        <v>1.145533262163288</v>
+        <v>0.6146431105920719</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-2.181852333843779</v>
+        <v>-0.1226210818960022</v>
       </c>
       <c r="C32">
-        <v>0.3734908950865103</v>
+        <v>0.8251955039880801</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.1119761216873711</v>
+        <v>-1.983281266346462</v>
       </c>
       <c r="C33">
-        <v>1.654729358940139</v>
+        <v>0.8477468647373405</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-1.736866131613524</v>
+        <v>-0.8845508977744343</v>
       </c>
       <c r="C34">
-        <v>0.4553549373499287</v>
+        <v>0.3241436239508425</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.1779460809266438</v>
+        <v>-0.4537732014314302</v>
       </c>
       <c r="C35">
-        <v>0.4338691813545729</v>
+        <v>-0.208335189381833</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.2033340437964464</v>
+        <v>0.4993271965539046</v>
       </c>
       <c r="C36">
-        <v>-0.02323703156504785</v>
+        <v>-0.2014301368970183</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.179209261013046</v>
+        <v>0.8387059573795717</v>
       </c>
       <c r="C37">
-        <v>0.05847873685166759</v>
+        <v>-0.7698009344363339</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.206214350722557</v>
+        <v>2.215115789544604</v>
       </c>
       <c r="C38">
-        <v>-0.9713528637707023</v>
+        <v>-2.364655637798234</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-2.124798578938335</v>
+        <v>-1.495978216931224</v>
       </c>
       <c r="C39">
-        <v>-1.672271615450662</v>
+        <v>0.9668282363199383</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.414915696571702</v>
+        <v>0.6856375712922929</v>
       </c>
       <c r="C40">
-        <v>1.224684964220211</v>
+        <v>-0.2928931896559084</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.8532792791271385</v>
+        <v>0.03719551638924795</v>
       </c>
       <c r="C41">
-        <v>0.6591208578935556</v>
+        <v>0.226404058097424</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.2509185461845737</v>
+        <v>0.5595379362796959</v>
       </c>
       <c r="C42">
-        <v>-1.13258035725977</v>
+        <v>0.1378480868901912</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.168098791487279</v>
+        <v>0.9786517790670003</v>
       </c>
       <c r="C43">
-        <v>-0.03133795955784169</v>
+        <v>2.345094302839654</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.195162023525188</v>
+        <v>1.035651541251337</v>
       </c>
       <c r="C44">
-        <v>-0.7407221483639517</v>
+        <v>0.1576439589107587</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.4530631588810621</v>
+        <v>1.080104801067911</v>
       </c>
       <c r="C45">
-        <v>-0.9526299455691484</v>
+        <v>-0.7217584796385981</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.4338473888081755</v>
+        <v>-0.2093162306387742</v>
       </c>
       <c r="C46">
-        <v>1.293450618376994</v>
+        <v>-1.530673916434384</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.117761497155274</v>
+        <v>0.6900555993733223</v>
       </c>
       <c r="C47">
-        <v>-0.4098705708579949</v>
+        <v>-1.34558273981689</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.6812669739785392</v>
+        <v>-0.3534808201312568</v>
       </c>
       <c r="C48">
-        <v>2.891395345700732</v>
+        <v>0.1838250802193236</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.02648095399745946</v>
+        <v>-1.814917596942307</v>
       </c>
       <c r="C49">
-        <v>0.1606736535083679</v>
+        <v>0.8928510506891864</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.036718740225758</v>
+        <v>0.5270015597024202</v>
       </c>
       <c r="C50">
-        <v>-0.2791496857265559</v>
+        <v>0.4658996010098939</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.2296360944230351</v>
+        <v>-0.1365035104475714</v>
       </c>
       <c r="C51">
-        <v>1.896573371781652</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-2.814770001482073</v>
-      </c>
-      <c r="C52">
-        <v>-2.322803380722585</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>0.4751168301144352</v>
-      </c>
-      <c r="C53">
-        <v>0.2038210035289623</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-0.9792164759846648</v>
-      </c>
-      <c r="C54">
-        <v>-0.7285276943257556</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-0.5025931976200138</v>
-      </c>
-      <c r="C55">
-        <v>0.1404270111552832</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-1.496024825618127</v>
-      </c>
-      <c r="C56">
-        <v>0.9517147113120304</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>-2.067342787089614</v>
-      </c>
-      <c r="C57">
-        <v>-1.571016226656623</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-0.8188966250082127</v>
-      </c>
-      <c r="C58">
-        <v>0.3160126741165257</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>0.1042797258169903</v>
-      </c>
-      <c r="C59">
-        <v>-0.7736573069643563</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>-1.167462881068342</v>
-      </c>
-      <c r="C60">
-        <v>1.29297325903997</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>1.045753836470287</v>
-      </c>
-      <c r="C61">
-        <v>0.4830112653192224</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>1.232626967581924</v>
-      </c>
-      <c r="C62">
-        <v>0.3811526199176897</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>1.812411907036035</v>
-      </c>
-      <c r="C63">
-        <v>0.3959215884529294</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.383673441328551</v>
-      </c>
-      <c r="C64">
-        <v>-0.2196422219878033</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>2.149248949228994</v>
-      </c>
-      <c r="C65">
-        <v>1.23118712021628</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.2448059659161321</v>
-      </c>
-      <c r="C66">
-        <v>-0.5436701780427626</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>1.276190850517245</v>
-      </c>
-      <c r="C67">
-        <v>1.565286481708737</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>1.511540905502317</v>
-      </c>
-      <c r="C68">
-        <v>0.4814818099365561</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>1.506441092225892</v>
-      </c>
-      <c r="C69">
-        <v>-0.2799352693821845</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-0.5217974723135208</v>
-      </c>
-      <c r="C70">
-        <v>-0.06008950021163112</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-0.7855772578850595</v>
-      </c>
-      <c r="C71">
-        <v>-0.472521742166337</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.2446514043811909</v>
-      </c>
-      <c r="C72">
-        <v>1.871130683339133</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>-1.666916279211855</v>
-      </c>
-      <c r="C73">
-        <v>-1.813977484543009</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>0.6920891109985635</v>
-      </c>
-      <c r="C74">
-        <v>1.718256324837287</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-2.215999273364845</v>
-      </c>
-      <c r="C75">
-        <v>-0.645070613698137</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>0.6324068752283344</v>
-      </c>
-      <c r="C76">
-        <v>0.4179304091912109</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.1775836258731319</v>
-      </c>
-      <c r="C77">
-        <v>-1.664045348116656</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-0.5963854008061782</v>
-      </c>
-      <c r="C78">
-        <v>-1.967511720723334</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>-1.458989044154635</v>
-      </c>
-      <c r="C79">
-        <v>1.148781921435985</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.4611164901612795</v>
-      </c>
-      <c r="C80">
-        <v>0.1489857300150305</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.5671940411935628</v>
-      </c>
-      <c r="C81">
-        <v>-0.7685318476287779</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.1771220020476018</v>
-      </c>
-      <c r="C82">
-        <v>1.439799051626481</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>0.3858654473948251</v>
-      </c>
-      <c r="C83">
-        <v>0.6460494190238579</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>-2.09699892292526</v>
-      </c>
-      <c r="C84">
-        <v>-0.07283525051020001</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-1.08076618005526</v>
-      </c>
-      <c r="C85">
-        <v>-0.5202717671655063</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-0.4669883486631667</v>
-      </c>
-      <c r="C86">
-        <v>0.1862945396038941</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>-1.02990616240328</v>
-      </c>
-      <c r="C87">
-        <v>1.004068148660568</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.4045954335972359</v>
-      </c>
-      <c r="C88">
-        <v>-1.099073071801165</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-0.5557132002059485</v>
-      </c>
-      <c r="C89">
-        <v>0.8135845761637548</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>0.8983620848575852</v>
-      </c>
-      <c r="C90">
-        <v>2.936220019379516</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>0.4526800704919036</v>
-      </c>
-      <c r="C91">
-        <v>0.6135153483390249</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>1.147306163664219</v>
-      </c>
-      <c r="C92">
-        <v>0.8721418481062863</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-1.422025209599646</v>
-      </c>
-      <c r="C93">
-        <v>0.8403257093110785</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.9808019744782094</v>
-      </c>
-      <c r="C94">
-        <v>-0.532525073213959</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>0.47138164694139</v>
-      </c>
-      <c r="C95">
-        <v>-0.2211038805835675</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>1.712384543473242</v>
-      </c>
-      <c r="C96">
-        <v>0.6561412236731187</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-0.3340890506865298</v>
-      </c>
-      <c r="C97">
-        <v>-0.1507503085949022</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-0.05766635040335309</v>
-      </c>
-      <c r="C98">
-        <v>-2.635586104407143</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>0.6619192860929757</v>
-      </c>
-      <c r="C99">
-        <v>-0.6724068231334515</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-0.06811068088886126</v>
-      </c>
-      <c r="C100">
-        <v>0.6584709584666456</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>-1.116262641416808</v>
-      </c>
-      <c r="C101">
-        <v>-1.322119599084269</v>
+        <v>0.0111238917194653</v>
       </c>
     </row>
   </sheetData>
